--- a/artfynd/A 22868-2026 artfynd.xlsx
+++ b/artfynd/A 22868-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1021,45 +1021,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134759318</v>
+        <v>135429537</v>
       </c>
       <c r="B5" t="n">
-        <v>106324</v>
+        <v>58136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468657</v>
+        <v>468677</v>
       </c>
       <c r="R5" t="n">
-        <v>6553259</v>
+        <v>6553239</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1086,22 +1095,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>19:20</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>19:20</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,6 +1124,113 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134759318</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>468657</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6553259</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22868-2026 artfynd.xlsx
+++ b/artfynd/A 22868-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134759312</v>
+        <v>135442637</v>
       </c>
       <c r="B2" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468657</v>
+        <v>468681</v>
       </c>
       <c r="R2" t="n">
-        <v>6553259</v>
+        <v>6553174</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>19:19</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>19:19</t>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Noterad 6 dagar totalt 6 ggr under 8-dagarsperioden.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134759721</v>
+        <v>134759312</v>
       </c>
       <c r="B3" t="n">
         <v>57162</v>
@@ -818,7 +813,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468674</v>
+        <v>468657</v>
       </c>
       <c r="R3" t="n">
-        <v>6553252</v>
+        <v>6553259</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -857,27 +852,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bälgrop</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,38 +894,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134761343</v>
+        <v>134759721</v>
       </c>
       <c r="B4" t="n">
-        <v>58136</v>
+        <v>57162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468678</v>
+        <v>468674</v>
       </c>
       <c r="R4" t="n">
-        <v>6553218</v>
+        <v>6553252</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -974,12 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>173 noteringar under perioden</t>
+          <t>Bälgrop</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,42 +1011,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135429537</v>
+        <v>135442573</v>
       </c>
       <c r="B5" t="n">
-        <v>58136</v>
+        <v>57776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102118</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1065,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468677</v>
+        <v>468681</v>
       </c>
       <c r="R5" t="n">
-        <v>6553239</v>
+        <v>6553174</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,12 +1086,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Noterad varje dag totalt 392 ggr under 8-dagarsperioden.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,45 +1123,59 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134759318</v>
+        <v>135442497</v>
       </c>
       <c r="B6" t="n">
-        <v>106324</v>
+        <v>58415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>102999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468657</v>
+        <v>468681</v>
       </c>
       <c r="R6" t="n">
-        <v>6553259</v>
+        <v>6553174</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1192,22 +1202,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>19:20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>19:20</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,6 +1231,560 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134761343</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>468678</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6553218</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>173 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135429537</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>468677</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6553239</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135442692</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>468681</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6553174</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Noterad 6 dagar totalt 102 ggr under 8-dagarsperioden.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135442710</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>468681</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6553174</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Noterad 7 dagar totalt 432 ggr under 8-dagarsperioden.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134759318</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>468657</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6553259</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22868-2026 artfynd.xlsx
+++ b/artfynd/A 22868-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1681,45 +1681,51 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134759318</v>
+        <v>135484569</v>
       </c>
       <c r="B11" t="n">
-        <v>106324</v>
+        <v>56833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>205998</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468657</v>
+        <v>468676</v>
       </c>
       <c r="R11" t="n">
-        <v>6553259</v>
+        <v>6553210</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1746,22 +1752,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,6 +1791,113 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134759318</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>468657</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6553259</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22868-2026 artfynd.xlsx
+++ b/artfynd/A 22868-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442637</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759312</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759721</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442573</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,6 +1256,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442497</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134761343</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429537</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1566,6 +1606,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442692</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1678,6 +1723,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442710</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1791,6 +1841,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484569</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1898,8 +1953,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134759318</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 22868-2026 artfynd.xlsx
+++ b/artfynd/A 22868-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135442637</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>135442573</v>
       </c>
       <c r="B5" t="n">
-        <v>57776</v>
+        <v>57781</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>135442497</v>
       </c>
       <c r="B6" t="n">
-        <v>58415</v>
+        <v>58420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>135429537</v>
       </c>
       <c r="B8" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135442692</v>
       </c>
       <c r="B9" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>135442710</v>
       </c>
       <c r="B10" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>135484569</v>
       </c>
       <c r="B11" t="n">
-        <v>56833</v>
+        <v>56838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22868-2026 artfynd.xlsx
+++ b/artfynd/A 22868-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134759312</v>
+        <v>135442637</v>
       </c>
       <c r="B2" t="n">
-        <v>57162</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468657</v>
+        <v>468681</v>
       </c>
       <c r="R2" t="n">
-        <v>6553259</v>
+        <v>6553174</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +750,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>19:19</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>19:19</t>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Noterad 6 dagar totalt 6 ggr under 8-dagarsperioden.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,13 +786,13 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134759312</t>
+          <t>https://artportalen.se/Sighting/135442637</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134759721</v>
+        <v>134759312</v>
       </c>
       <c r="B3" t="n">
         <v>57162</v>
@@ -828,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468674</v>
+        <v>468657</v>
       </c>
       <c r="R3" t="n">
-        <v>6553252</v>
+        <v>6553259</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -867,27 +862,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bälgrop</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,44 +903,44 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134759721</t>
+          <t>https://artportalen.se/Sighting/134759312</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134761343</v>
+        <v>134759721</v>
       </c>
       <c r="B4" t="n">
-        <v>58136</v>
+        <v>57162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468678</v>
+        <v>468674</v>
       </c>
       <c r="R4" t="n">
-        <v>6553218</v>
+        <v>6553252</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -989,12 +979,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>173 noteringar under perioden</t>
+          <t>Bälgrop</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,16 +1025,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134761343</t>
+          <t>https://artportalen.se/Sighting/134759721</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134759318</v>
+        <v>135442573</v>
       </c>
       <c r="B5" t="n">
-        <v>106324</v>
+        <v>57781</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,37 +1042,47 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>102118</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468657</v>
+        <v>468681</v>
       </c>
       <c r="R5" t="n">
-        <v>6553259</v>
+        <v>6553174</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,22 +1106,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>19:20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>19:20</t>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Noterad varje dag totalt 392 ggr under 8-dagarsperioden.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,6 +1141,819 @@
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442573</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135442497</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58420</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>468681</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6553174</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442497</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134761343</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>468678</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6553218</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>173 noteringar under perioden</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134761343</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135429537</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>468677</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6553239</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429537</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135442692</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>468681</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6553174</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Noterad 6 dagar totalt 102 ggr under 8-dagarsperioden.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442692</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135442710</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>468681</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6553174</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Noterad 7 dagar totalt 432 ggr under 8-dagarsperioden.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135442710</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135484569</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56838</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>468676</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6553210</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>23:05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>23:05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484569</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134759318</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Björnbråtstjärnen, Björnbråtstjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>468657</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6553259</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134759318</t>
         </is>
@@ -1157,6 +1965,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
